--- a/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -21,9 +21,27 @@
     <x:t>FName</x:t>
   </x:si>
   <x:si>
+    <x:t>John</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dagny</x:t>
+  </x:si>
+  <x:si>
     <x:t>LName</x:t>
   </x:si>
   <x:si>
+    <x:t>Galt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rearden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taggart</x:t>
+  </x:si>
+  <x:si>
     <x:t>Outcast</x:t>
   </x:si>
   <x:si>
@@ -36,40 +54,22 @@
     <x:t>Age</x:t>
   </x:si>
   <x:si>
+    <x:t>Sum Of Income</x:t>
+  </x:si>
+  <x:si>
     <x:t>Table Headers</x:t>
   </x:si>
   <x:si>
     <x:t>Names</x:t>
   </x:si>
   <x:si>
-    <x:t>John</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Galt</x:t>
-  </x:si>
-  <x:si>
     <x:t>John Galt</x:t>
   </x:si>
   <x:si>
-    <x:t>Hank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rearden</x:t>
-  </x:si>
-  <x:si>
     <x:t>Hank Rearden</x:t>
   </x:si>
   <x:si>
-    <x:t>Dagny</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Taggart</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dagny Taggart</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sum Of Income</x:t>
   </x:si>
   <x:si>
     <x:t>Contacts</x:t>
@@ -821,33 +821,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="15" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="16" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="B3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D3" s="0" t="b">
         <x:v>1</x:v>
@@ -865,15 +865,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="B4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D4" s="0" t="b">
         <x:v>0</x:v>
@@ -888,18 +888,18 @@
         <x:f>(DATE(2017, 10, 3) - E4) / 365</x:f>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="B5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="0" t="b">
         <x:v>0</x:v>
@@ -914,15 +914,15 @@
         <x:f>(DATE(2017, 10, 3) - E5) / 365</x:f>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="B6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E6" s="15"/>
       <x:c r="F6" s="16">
@@ -932,17 +932,17 @@
         <x:f>SUBTOTAL(101,[Age])</x:f>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="I7" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="I8" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -989,33 +989,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="15" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="16" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="B3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D3" s="0" t="b">
         <x:v>1</x:v>
@@ -1033,15 +1033,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
       <x:c r="B4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D4" s="0" t="b">
         <x:v>0</x:v>
@@ -1056,18 +1056,18 @@
         <x:f>(DATE(2017, 10, 3) - E4) / 365</x:f>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="B5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="0" t="b">
         <x:v>0</x:v>
@@ -1082,15 +1082,15 @@
         <x:f>(DATE(2017, 10, 3) - E5) / 365</x:f>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="B6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E6" s="15"/>
       <x:c r="F6" s="16">
@@ -1100,17 +1100,17 @@
         <x:f>SUBTOTAL(101,[Age])</x:f>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="I7" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="I8" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -1168,24 +1168,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D3" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E3" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
       <x:c r="B4" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="8" t="s">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D4" s="8" t="b">
         <x:v>1</x:v>
@@ -1199,10 +1199,10 @@
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="B5" s="7" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="8" t="s">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="8" t="b">
         <x:v>0</x:v>
@@ -1216,10 +1216,10 @@
     </x:row>
     <x:row r="6" spans="1:6">
       <x:c r="B6" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D6" s="12" t="b">
         <x:v>0</x:v>

--- a/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -797,33 +797,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:F6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="6.853482" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16.139196" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13.853482" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="3.710625" customWidth="1"/>
+    <x:col min="2" max="2" width="14.710625" customWidth="1"/>
+    <x:col min="3" max="3" width="9.567768" customWidth="1"/>
+    <x:col min="4" max="4" width="10.282054" customWidth="1"/>
+    <x:col min="5" max="5" width="10.139196" customWidth="1"/>
+    <x:col min="6" max="6" width="9.996339" customWidth="1"/>
+    <x:col min="7" max="7" width="6.853482" customWidth="1"/>
+    <x:col min="8" max="8" width="3.710625" customWidth="1"/>
+    <x:col min="9" max="9" width="16.139196" customWidth="1"/>
+    <x:col min="10" max="10" width="3.710625" customWidth="1"/>
+    <x:col min="11" max="11" width="13.853482" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:11">
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="15" t="s">
@@ -832,24 +829,24 @@
       <x:c r="F2" s="16" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="G2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="I2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
+      <x:c r="K2" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="b">
+      <x:c r="D3" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E3" s="15">
@@ -861,21 +858,21 @@
       <x:c r="G3" s="17">
         <x:f>(DATE(2017, 10, 3) - E3) / 365</x:f>
       </x:c>
-      <x:c r="I3" s="0" t="s">
+      <x:c r="I3" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K3" s="0" t="s">
+      <x:c r="K3" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="b">
+      <x:c r="D4" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="15">
@@ -887,21 +884,21 @@
       <x:c r="G4" s="17">
         <x:f>(DATE(2017, 10, 3) - E4) / 365</x:f>
       </x:c>
-      <x:c r="I4" s="0" t="s">
+      <x:c r="I4" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
+      <x:c r="K4" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="b">
+      <x:c r="D5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="15">
@@ -913,15 +910,15 @@
       <x:c r="G5" s="17">
         <x:f>(DATE(2017, 10, 3) - E5) / 365</x:f>
       </x:c>
-      <x:c r="I5" s="0" t="s">
+      <x:c r="I5" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
+      <x:c r="K5" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E6" s="15"/>
@@ -931,30 +928,27 @@
       <x:c r="G6" s="17">
         <x:f>SUBTOTAL(101,[Age])</x:f>
       </x:c>
-      <x:c r="I6" s="0" t="s">
+      <x:c r="I6" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
-      <x:c r="I7" s="0" t="s">
+      <x:c r="I7" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
-      <x:c r="I8" s="0" t="s">
+      <x:c r="I8" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
-      <x:c r="I9" s="0" t="str">
+      <x:c r="I9" t="str">
         <x:f>CONCATENATE("Count: ", CountA(Headers[Table Headers]))</x:f>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="3">
     <x:tablePart r:id="rId5"/>
     <x:tablePart r:id="rId7"/>
@@ -965,33 +959,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:K9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="6.853482" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16.139196" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13.853482" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="3.710625" customWidth="1"/>
+    <x:col min="2" max="2" width="14.710625" customWidth="1"/>
+    <x:col min="3" max="3" width="9.567768" customWidth="1"/>
+    <x:col min="4" max="4" width="10.282054" customWidth="1"/>
+    <x:col min="5" max="5" width="10.139196" customWidth="1"/>
+    <x:col min="6" max="6" width="9.996339" customWidth="1"/>
+    <x:col min="7" max="7" width="6.853482" customWidth="1"/>
+    <x:col min="8" max="8" width="3.710625" customWidth="1"/>
+    <x:col min="9" max="9" width="16.139196" customWidth="1"/>
+    <x:col min="10" max="10" width="3.710625" customWidth="1"/>
+    <x:col min="11" max="11" width="13.853482" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:11">
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="15" t="s">
@@ -1000,24 +991,24 @@
       <x:c r="F2" s="16" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="G2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="I2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
+      <x:c r="K2" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:11">
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="b">
+      <x:c r="D3" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E3" s="15">
@@ -1029,21 +1020,21 @@
       <x:c r="G3" s="17">
         <x:f>(DATE(2017, 10, 3) - E3) / 365</x:f>
       </x:c>
-      <x:c r="I3" s="0" t="s">
+      <x:c r="I3" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K3" s="0" t="s">
+      <x:c r="K3" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:11">
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="b">
+      <x:c r="D4" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="15">
@@ -1055,21 +1046,21 @@
       <x:c r="G4" s="17">
         <x:f>(DATE(2017, 10, 3) - E4) / 365</x:f>
       </x:c>
-      <x:c r="I4" s="0" t="s">
+      <x:c r="I4" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
+      <x:c r="K4" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11">
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="b">
+      <x:c r="D5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="15">
@@ -1081,15 +1072,15 @@
       <x:c r="G5" s="17">
         <x:f>(DATE(2017, 10, 3) - E5) / 365</x:f>
       </x:c>
-      <x:c r="I5" s="0" t="s">
+      <x:c r="I5" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
+      <x:c r="K5" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E6" s="15"/>
@@ -1099,37 +1090,27 @@
       <x:c r="G6" s="17">
         <x:f>SUBTOTAL(101,[Age])</x:f>
       </x:c>
-      <x:c r="I6" s="0" t="s">
+      <x:c r="I6" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
-      <x:c r="I7" s="0" t="s">
+      <x:c r="I7" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
-      <x:c r="I8" s="0" t="s">
+      <x:c r="I8" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
-      <x:c r="I9" s="0" t="str">
+      <x:c r="I9" t="str">
         <x:f>CONCATENATE("Count: ", CountA(Headers[Table Headers]))</x:f>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="3">
     <x:tablePart r:id="rId12"/>
     <x:tablePart r:id="rId13"/>
@@ -1140,18 +1121,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:F6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.424911" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.139196" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="2" max="2" width="7.424911" customWidth="1"/>
+    <x:col min="3" max="3" width="8.567768" customWidth="1"/>
+    <x:col min="4" max="4" width="8.139196" customWidth="1"/>
+    <x:col min="5" max="5" width="10.139196" customWidth="1"/>
+    <x:col min="6" max="6" width="8.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">
@@ -1235,17 +1213,6 @@
   <x:mergeCells count="1">
     <x:mergeCell ref="B2:F2"/>
   </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -801,16 +801,16 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.710625" customWidth="1"/>
-    <x:col min="2" max="2" width="14.710625" customWidth="1"/>
-    <x:col min="3" max="3" width="9.567768" customWidth="1"/>
-    <x:col min="4" max="4" width="10.282054" customWidth="1"/>
-    <x:col min="5" max="5" width="10.139196" customWidth="1"/>
-    <x:col min="6" max="6" width="9.996339" customWidth="1"/>
+    <x:col min="2" max="2" width="14.282054" customWidth="1"/>
+    <x:col min="3" max="3" width="9.282054" customWidth="1"/>
+    <x:col min="4" max="4" width="9.996339" customWidth="1"/>
+    <x:col min="5" max="5" width="9.853482" customWidth="1"/>
+    <x:col min="6" max="6" width="9.710625" customWidth="1"/>
     <x:col min="7" max="7" width="6.853482" customWidth="1"/>
     <x:col min="8" max="8" width="3.710625" customWidth="1"/>
-    <x:col min="9" max="9" width="16.139196" customWidth="1"/>
+    <x:col min="9" max="9" width="15.710625" customWidth="1"/>
     <x:col min="10" max="10" width="3.710625" customWidth="1"/>
-    <x:col min="11" max="11" width="13.853482" customWidth="1"/>
+    <x:col min="11" max="11" width="13.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:11">
@@ -963,16 +963,16 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.710625" customWidth="1"/>
-    <x:col min="2" max="2" width="14.710625" customWidth="1"/>
-    <x:col min="3" max="3" width="9.567768" customWidth="1"/>
-    <x:col min="4" max="4" width="10.282054" customWidth="1"/>
-    <x:col min="5" max="5" width="10.139196" customWidth="1"/>
-    <x:col min="6" max="6" width="9.996339" customWidth="1"/>
+    <x:col min="2" max="2" width="14.282054" customWidth="1"/>
+    <x:col min="3" max="3" width="9.282054" customWidth="1"/>
+    <x:col min="4" max="4" width="9.996339" customWidth="1"/>
+    <x:col min="5" max="5" width="9.853482" customWidth="1"/>
+    <x:col min="6" max="6" width="9.710625" customWidth="1"/>
     <x:col min="7" max="7" width="6.853482" customWidth="1"/>
     <x:col min="8" max="8" width="3.710625" customWidth="1"/>
-    <x:col min="9" max="9" width="16.139196" customWidth="1"/>
+    <x:col min="9" max="9" width="15.710625" customWidth="1"/>
     <x:col min="10" max="10" width="3.710625" customWidth="1"/>
-    <x:col min="11" max="11" width="13.853482" customWidth="1"/>
+    <x:col min="11" max="11" width="13.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:11">
@@ -1125,11 +1125,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="7.424911" customWidth="1"/>
-    <x:col min="3" max="3" width="8.567768" customWidth="1"/>
-    <x:col min="4" max="4" width="8.139196" customWidth="1"/>
-    <x:col min="5" max="5" width="10.139196" customWidth="1"/>
-    <x:col min="6" max="6" width="8.710625" customWidth="1"/>
+    <x:col min="2" max="2" width="7.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="8.282054" customWidth="1"/>
+    <x:col min="4" max="4" width="7.853482" customWidth="1"/>
+    <x:col min="5" max="5" width="9.853482" customWidth="1"/>
+    <x:col min="6" max="6" width="8.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">

--- a/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CopyingWorksheets.xlsx
@@ -800,17 +800,17 @@
   <x:dimension ref="A1:F6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="3.710625" customWidth="1"/>
-    <x:col min="2" max="2" width="14.282054" customWidth="1"/>
-    <x:col min="3" max="3" width="9.282054" customWidth="1"/>
-    <x:col min="4" max="4" width="9.996339" customWidth="1"/>
-    <x:col min="5" max="5" width="9.853482" customWidth="1"/>
-    <x:col min="6" max="6" width="9.710625" customWidth="1"/>
-    <x:col min="7" max="7" width="6.853482" customWidth="1"/>
-    <x:col min="8" max="8" width="3.710625" customWidth="1"/>
-    <x:col min="9" max="9" width="15.710625" customWidth="1"/>
-    <x:col min="10" max="10" width="3.710625" customWidth="1"/>
-    <x:col min="11" max="11" width="13.424911" customWidth="1"/>
+    <x:col min="1" max="1" width="3.714286" customWidth="1"/>
+    <x:col min="2" max="2" width="14.285714" customWidth="1"/>
+    <x:col min="3" max="3" width="9.285714" customWidth="1"/>
+    <x:col min="4" max="4" width="10" customWidth="1"/>
+    <x:col min="5" max="5" width="9.857143" customWidth="1"/>
+    <x:col min="6" max="6" width="9.714286" customWidth="1"/>
+    <x:col min="7" max="7" width="6.857143" customWidth="1"/>
+    <x:col min="8" max="8" width="3.714286" customWidth="1"/>
+    <x:col min="9" max="9" width="15.714286" customWidth="1"/>
+    <x:col min="10" max="10" width="3.714286" customWidth="1"/>
+    <x:col min="11" max="11" width="13.428571" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:11">
@@ -962,17 +962,17 @@
   <x:dimension ref="A1:K9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="3.710625" customWidth="1"/>
-    <x:col min="2" max="2" width="14.282054" customWidth="1"/>
-    <x:col min="3" max="3" width="9.282054" customWidth="1"/>
-    <x:col min="4" max="4" width="9.996339" customWidth="1"/>
-    <x:col min="5" max="5" width="9.853482" customWidth="1"/>
-    <x:col min="6" max="6" width="9.710625" customWidth="1"/>
-    <x:col min="7" max="7" width="6.853482" customWidth="1"/>
-    <x:col min="8" max="8" width="3.710625" customWidth="1"/>
-    <x:col min="9" max="9" width="15.710625" customWidth="1"/>
-    <x:col min="10" max="10" width="3.710625" customWidth="1"/>
-    <x:col min="11" max="11" width="13.424911" customWidth="1"/>
+    <x:col min="1" max="1" width="3.714286" customWidth="1"/>
+    <x:col min="2" max="2" width="14.285714" customWidth="1"/>
+    <x:col min="3" max="3" width="9.285714" customWidth="1"/>
+    <x:col min="4" max="4" width="10" customWidth="1"/>
+    <x:col min="5" max="5" width="9.857143" customWidth="1"/>
+    <x:col min="6" max="6" width="9.714286" customWidth="1"/>
+    <x:col min="7" max="7" width="6.857143" customWidth="1"/>
+    <x:col min="8" max="8" width="3.714286" customWidth="1"/>
+    <x:col min="9" max="9" width="15.714286" customWidth="1"/>
+    <x:col min="10" max="10" width="3.714286" customWidth="1"/>
+    <x:col min="11" max="11" width="13.428571" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:11">
@@ -1124,12 +1124,12 @@
   <x:dimension ref="A1:F6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="7.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="8.282054" customWidth="1"/>
-    <x:col min="4" max="4" width="7.853482" customWidth="1"/>
-    <x:col min="5" max="5" width="9.853482" customWidth="1"/>
-    <x:col min="6" max="6" width="8.424911" customWidth="1"/>
+    <x:col min="1" max="1" width="9.144286"/>
+    <x:col min="2" max="2" width="7.142857" customWidth="1"/>
+    <x:col min="3" max="3" width="8.285714" customWidth="1"/>
+    <x:col min="4" max="4" width="7.857143" customWidth="1"/>
+    <x:col min="5" max="5" width="9.857143" customWidth="1"/>
+    <x:col min="6" max="6" width="8.428571" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">
